--- a/ONCHO/OEM/Congo/2022 jul/cg_oncho_oem_1_site_participant_202207.xlsx
+++ b/ONCHO/OEM/Congo/2022 jul/cg_oncho_oem_1_site_participant_202207.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\OEM\Congo\2022 jul\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1993D1-F38C-463C-9606-BB14ADB77942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="500"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -15,7 +21,20 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -274,9 +293,6 @@
     <t>is_natif</t>
   </si>
   <si>
-    <t>La participation est-il originaire du village (né au village) ou migrant (n'est pas née au village et est venu s'installer)</t>
-  </si>
-  <si>
     <t>${consent} = 'Oui'  and ${add_participant} = 'Oui'</t>
   </si>
   <si>
@@ -464,19 +480,16 @@
   </si>
   <si>
     <t>District</t>
+  </si>
+  <si>
+    <t>Le participant est-il originaire du village (né au village) ou migrant (n'est pas née au village et est venu s'installer)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -519,152 +532,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,194 +558,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -916,265 +599,23 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.14996795556505"/>
+        <color theme="0" tint="-0.14993743705557422"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.14996795556505"/>
+        <color theme="0" tint="-0.14993743705557422"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.14996795556505"/>
+        <color theme="0" tint="-0.14993743705557422"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="0" tint="-0.14993743705557422"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1228,195 +669,31 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 10" xfId="1"/>
-    <cellStyle name="60% - Accent6" xfId="2" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="3" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="4" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="5" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="6" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="7" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="9" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="10" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="11" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="14" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="15" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="16" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="17" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="18" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="19" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="20" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="21" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="22" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="23" builtinId="32"/>
-    <cellStyle name="Bad" xfId="24" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="25" builtinId="42"/>
-    <cellStyle name="Total" xfId="26" builtinId="25"/>
-    <cellStyle name="Output" xfId="27" builtinId="21"/>
-    <cellStyle name="Currency" xfId="28" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="29" builtinId="38"/>
-    <cellStyle name="Note" xfId="30" builtinId="10"/>
-    <cellStyle name="Input" xfId="31" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="32" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="33" builtinId="22"/>
-    <cellStyle name="Good" xfId="34" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="35" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="36" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="37" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="38" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="Title" xfId="40" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="41" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="42" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="43" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="44" builtinId="17"/>
-    <cellStyle name="Comma" xfId="45" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="46" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="47" builtinId="40"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="49" builtinId="8"/>
+    <cellStyle name="Normal 2 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="INTRO"/>
       <sheetName val="COUNTRY_INFO"/>
-      <sheetName val="MDA1"/>
-      <sheetName val="MDA4"/>
-      <sheetName val="MDA3"/>
-      <sheetName val="T1"/>
-      <sheetName val="T2"/>
-      <sheetName val="T3_R1"/>
-      <sheetName val="T3_R2"/>
-      <sheetName val="DISTRICT"/>
-      <sheetName val="SUMMARY"/>
-      <sheetName val="PROFILE"/>
-      <sheetName val="DATA_POLICY"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>Congo</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1674,31 +951,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="19.6296296296296" customWidth="1"/>
+    <col min="1" max="1" width="19.625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="47.5037037037037" customWidth="1"/>
-    <col min="4" max="4" width="47.3703703703704" customWidth="1"/>
-    <col min="5" max="5" width="12.6296296296296" customWidth="1"/>
-    <col min="6" max="6" width="16.8740740740741" customWidth="1"/>
-    <col min="7" max="7" width="29.5037037037037" customWidth="1"/>
-    <col min="8" max="8" width="28.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="12.6296296296296" customWidth="1"/>
-    <col min="10" max="10" width="9.75555555555556" customWidth="1"/>
-    <col min="11" max="11" width="35.3703703703704" customWidth="1"/>
-    <col min="12" max="12" width="13.8740740740741" customWidth="1"/>
-    <col min="13" max="13" width="36.6296296296296" customWidth="1"/>
+    <col min="3" max="3" width="47.5" customWidth="1"/>
+    <col min="4" max="4" width="47.375" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="29.5" customWidth="1"/>
+    <col min="8" max="8" width="76" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="11" width="35.375" customWidth="1"/>
+    <col min="12" max="12" width="13.875" customWidth="1"/>
+    <col min="13" max="13" width="36.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" ht="18" spans="1:14">
+    <row r="1" spans="1:14" s="7" customFormat="1" ht="18.75">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1742,7 +1019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="7" customFormat="1" spans="1:13">
+    <row r="2" spans="1:14" s="7" customFormat="1">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -1771,7 +1048,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" s="7" customFormat="1" spans="1:12">
+    <row r="3" spans="1:14" s="7" customFormat="1">
       <c r="A3" s="21" t="s">
         <v>21</v>
       </c>
@@ -1793,7 +1070,7 @@
       <c r="K3" s="20"/>
       <c r="L3" s="20"/>
     </row>
-    <row r="4" s="7" customFormat="1" spans="1:13">
+    <row r="4" spans="1:14" s="7" customFormat="1">
       <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
@@ -1817,7 +1094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" spans="1:13">
+    <row r="5" spans="1:14" s="7" customFormat="1">
       <c r="A5" s="7" t="s">
         <v>28</v>
       </c>
@@ -1840,7 +1117,7 @@
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
     </row>
-    <row r="6" s="7" customFormat="1" spans="1:13">
+    <row r="6" spans="1:14" s="7" customFormat="1">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -1867,7 +1144,7 @@
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1881,7 +1158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
+    <row r="8" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -1908,7 +1185,7 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
+    <row r="9" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>43</v>
       </c>
@@ -1933,7 +1210,7 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
     </row>
-    <row r="10" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
+    <row r="10" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>43</v>
       </c>
@@ -1958,7 +1235,7 @@
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" s="18" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
+    <row r="11" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>49</v>
       </c>
@@ -1981,7 +1258,7 @@
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
     </row>
-    <row r="12" s="7" customFormat="1" spans="1:10">
+    <row r="12" spans="1:14" s="7" customFormat="1">
       <c r="A12" s="7" t="s">
         <v>52</v>
       </c>
@@ -1994,7 +1271,7 @@
       <c r="D12" s="21"/>
       <c r="J12" s="20"/>
     </row>
-    <row r="13" s="7" customFormat="1" spans="1:10">
+    <row r="13" spans="1:14" s="7" customFormat="1">
       <c r="A13" s="7" t="s">
         <v>55</v>
       </c>
@@ -2009,7 +1286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" s="7" customFormat="1" spans="1:10">
+    <row r="14" spans="1:14" s="7" customFormat="1">
       <c r="A14" s="7" t="s">
         <v>55</v>
       </c>
@@ -2027,7 +1304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" spans="1:10">
+    <row r="15" spans="1:14" s="7" customFormat="1">
       <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
@@ -2045,7 +1322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" s="7" customFormat="1" spans="1:10">
+    <row r="16" spans="1:14" s="7" customFormat="1">
       <c r="A16" s="7" t="s">
         <v>65</v>
       </c>
@@ -2063,7 +1340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" s="7" customFormat="1" spans="1:10">
+    <row r="17" spans="1:10" s="7" customFormat="1">
       <c r="A17" s="7" t="s">
         <v>68</v>
       </c>
@@ -2081,7 +1358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" s="7" customFormat="1" ht="42.75" spans="1:10">
+    <row r="18" spans="1:10" s="7" customFormat="1" ht="47.25">
       <c r="A18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2099,7 +1376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" s="7" customFormat="1" spans="1:10">
+    <row r="19" spans="1:10" s="7" customFormat="1">
       <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
@@ -2125,7 +1402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" s="7" customFormat="1" spans="1:10">
+    <row r="20" spans="1:10" s="7" customFormat="1">
       <c r="A20" s="7" t="s">
         <v>55</v>
       </c>
@@ -2143,7 +1420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" s="7" customFormat="1" ht="28.5" spans="1:10">
+    <row r="21" spans="1:10" s="7" customFormat="1" ht="47.25">
       <c r="A21" s="7" t="s">
         <v>55</v>
       </c>
@@ -2151,82 +1428,82 @@
         <v>83</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="D21" s="21"/>
       <c r="H21" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" s="7" customFormat="1" spans="1:10">
+    <row r="22" spans="1:10" s="7" customFormat="1">
       <c r="A22" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="D22" s="21"/>
       <c r="G22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="J22" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" s="7" customFormat="1" spans="1:10">
+    <row r="23" spans="1:10" s="7" customFormat="1">
       <c r="A23" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>91</v>
       </c>
       <c r="D23" s="21"/>
       <c r="H23" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" s="7" customFormat="1" spans="1:10">
+    <row r="25" spans="1:10" s="7" customFormat="1" ht="31.5">
       <c r="A25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="C25" s="21" t="s">
         <v>93</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>94</v>
       </c>
       <c r="D25" s="21"/>
       <c r="H25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="7" customFormat="1" spans="1:10">
+    <row r="26" spans="1:10" s="7" customFormat="1">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>97</v>
       </c>
       <c r="D26" s="21"/>
       <c r="H26" s="7" t="s">
@@ -2236,45 +1513,45 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" s="7" customFormat="1" spans="1:10">
+    <row r="27" spans="1:10" s="7" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" s="7" customFormat="1" spans="1:10">
+    <row r="28" spans="1:10" s="7" customFormat="1">
       <c r="A28" s="7" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" s="21"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" s="7" customFormat="1" spans="1:8">
+    <row r="29" spans="1:10" s="7" customFormat="1">
       <c r="A29" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>100</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>101</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
       <c r="H29" s="18"/>
     </row>
-    <row r="30" s="7" customFormat="1" spans="1:8">
+    <row r="30" spans="1:10" s="7" customFormat="1">
       <c r="A30" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>102</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>103</v>
       </c>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -2283,25 +1560,23 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="16.3703703703704" customWidth="1"/>
-    <col min="2" max="2" width="39.6296296296296" customWidth="1"/>
-    <col min="3" max="3" width="23.7555555555556" customWidth="1"/>
-    <col min="4" max="4" width="11.7555555555556" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="39.625" customWidth="1"/>
+    <col min="3" max="3" width="23.75" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -2310,779 +1585,774 @@
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" customFormat="1" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="16"/>
     </row>
-    <row r="3" customFormat="1" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="16"/>
     </row>
-    <row r="4" customFormat="1" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>109</v>
-      </c>
       <c r="C4" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="17"/>
     </row>
-    <row r="5" customFormat="1" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" customFormat="1" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>111</v>
-      </c>
       <c r="C6" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="17"/>
     </row>
-    <row r="7" customFormat="1" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="17"/>
     </row>
-    <row r="8" s="8" customFormat="1" spans="1:5">
+    <row r="8" spans="1:5" s="8" customFormat="1">
       <c r="A8" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="17"/>
     </row>
-    <row r="9" s="8" customFormat="1" spans="1:5">
+    <row r="9" spans="1:5" s="8" customFormat="1">
       <c r="A9" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="17"/>
     </row>
-    <row r="10" customFormat="1" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="13"/>
       <c r="D10" s="11"/>
       <c r="E10" s="17"/>
     </row>
-    <row r="11" s="8" customFormat="1" spans="1:5">
+    <row r="11" spans="1:5" s="8" customFormat="1">
       <c r="A11" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="17"/>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:5">
+    <row r="12" spans="1:5" s="8" customFormat="1">
       <c r="A12" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="17"/>
     </row>
-    <row r="13" s="8" customFormat="1" spans="1:5">
+    <row r="13" spans="1:5" s="8" customFormat="1">
       <c r="A13" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="17"/>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:5">
+    <row r="14" spans="1:5" s="8" customFormat="1">
       <c r="A14" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="17"/>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:5">
+    <row r="15" spans="1:5" s="8" customFormat="1">
       <c r="A15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" spans="1:5" s="8" customFormat="1">
+      <c r="A16" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" spans="1:5" s="8" customFormat="1">
+      <c r="A17" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" spans="1:5" s="8" customFormat="1">
+      <c r="A18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="1:5" s="8" customFormat="1">
+      <c r="A19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="17"/>
+    </row>
+    <row r="20" spans="1:5" s="8" customFormat="1">
+      <c r="A20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" s="8" customFormat="1" spans="1:5">
-      <c r="A16" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" spans="1:5" s="8" customFormat="1">
+      <c r="A21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" s="8" customFormat="1" spans="1:5">
-      <c r="A17" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" s="8" customFormat="1" spans="1:5">
-      <c r="A18" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" s="8" customFormat="1" spans="1:5">
-      <c r="A19" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" s="8" customFormat="1" spans="1:5">
-      <c r="A20" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="1:5" s="8" customFormat="1">
+      <c r="A22" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="17"/>
-    </row>
-    <row r="21" s="8" customFormat="1" spans="1:5">
-      <c r="A21" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="E22" s="17"/>
+    </row>
+    <row r="23" spans="1:5" s="8" customFormat="1">
+      <c r="A23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" s="8" customFormat="1" spans="1:5">
-      <c r="A22" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="E23" s="17"/>
+    </row>
+    <row r="24" spans="1:5" s="8" customFormat="1">
+      <c r="A24" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" s="17"/>
+    </row>
+    <row r="25" spans="1:5" s="8" customFormat="1">
+      <c r="A25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" s="8" customFormat="1">
+      <c r="A26" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="17"/>
+    </row>
+    <row r="27" spans="1:5" s="8" customFormat="1">
+      <c r="A27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="17"/>
-    </row>
-    <row r="23" s="8" customFormat="1" spans="1:5">
-      <c r="A23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" s="11" t="s">
+      <c r="E27" s="17"/>
+    </row>
+    <row r="28" spans="1:5" s="8" customFormat="1">
+      <c r="A28" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" s="8" customFormat="1" spans="1:5">
-      <c r="A24" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="E28" s="17"/>
+    </row>
+    <row r="29" spans="1:5" s="8" customFormat="1">
+      <c r="A29" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="17"/>
-    </row>
-    <row r="25" s="8" customFormat="1" spans="1:5">
-      <c r="A25" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="E29" s="17"/>
+    </row>
+    <row r="30" spans="1:5" s="8" customFormat="1">
+      <c r="A30" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="17"/>
-    </row>
-    <row r="26" s="8" customFormat="1" spans="1:5">
-      <c r="A26" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="11" t="s">
+      <c r="E30" s="17"/>
+    </row>
+    <row r="31" spans="1:5" s="8" customFormat="1">
+      <c r="A31" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="17"/>
-    </row>
-    <row r="27" s="8" customFormat="1" spans="1:5">
-      <c r="A27" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="E31" s="17"/>
+    </row>
+    <row r="32" spans="1:5" s="8" customFormat="1">
+      <c r="A32" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="17"/>
-    </row>
-    <row r="28" s="8" customFormat="1" spans="1:5">
-      <c r="A28" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="B32" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="17"/>
+    </row>
+    <row r="33" spans="1:5" s="8" customFormat="1">
+      <c r="A33" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="17"/>
-    </row>
-    <row r="29" s="8" customFormat="1" spans="1:5">
-      <c r="A29" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="17"/>
-    </row>
-    <row r="30" s="8" customFormat="1" spans="1:5">
-      <c r="A30" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="17"/>
-    </row>
-    <row r="31" s="8" customFormat="1" spans="1:5">
-      <c r="A31" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="17"/>
-    </row>
-    <row r="32" s="8" customFormat="1" spans="1:5">
-      <c r="A32" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="B33" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="17"/>
-    </row>
-    <row r="33" s="8" customFormat="1" spans="1:5">
-      <c r="A33" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>138</v>
-      </c>
       <c r="D33" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E33" s="17"/>
     </row>
   </sheetData>
-  <sortState ref="A10:E46">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:E46">
     <sortCondition ref="B10:B46"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="46.1259259259259" customWidth="1"/>
+    <col min="1" max="1" width="46.125" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="15.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>143</v>
-      </c>
-      <c r="C2" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="14.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="10.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="2" t="e">
         <f>IF([1]COUNTRY_INFO!A9=0," ",[1]COUNTRY_INFO!A9)</f>
-        <v>Congo</v>
+        <v>#REF!</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A10=0," ",[1]COUNTRY_INFO!A10)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A11=0," ",[1]COUNTRY_INFO!A11)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A12=0," ",[1]COUNTRY_INFO!A12)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A13=0," ",[1]COUNTRY_INFO!A13)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A32=0," ",[1]COUNTRY_INFO!A32)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A10=0," ",[1]COUNTRY_INFO!A10)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A33=0," ",[1]COUNTRY_INFO!A33)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A36=0," ",[1]COUNTRY_INFO!A36)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A11=0," ",[1]COUNTRY_INFO!A11)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A37=0," ",[1]COUNTRY_INFO!A37)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="45">
+      <c r="A11" s="3" t="e">
+        <f>IF([1]COUNTRY_INFO!A38=0," ",[1]COUNTRY_INFO!A38)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A39=0," ",[1]COUNTRY_INFO!A39)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A40=0," ",[1]COUNTRY_INFO!A40)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A52=0," ",[1]COUNTRY_INFO!A52)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A12=0," ",[1]COUNTRY_INFO!A12)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A13=0," ",[1]COUNTRY_INFO!A13)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A32=0," ",[1]COUNTRY_INFO!A32)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A33=0," ",[1]COUNTRY_INFO!A33)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A36=0," ",[1]COUNTRY_INFO!A36)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A53=0," ",[1]COUNTRY_INFO!A53)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A37=0," ",[1]COUNTRY_INFO!A37)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A54=0," ",[1]COUNTRY_INFO!A54)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75" spans="1:3">
-      <c r="A11" s="3" t="str">
-        <f>IF([1]COUNTRY_INFO!A38=0," ",[1]COUNTRY_INFO!A38)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A55=0," ",[1]COUNTRY_INFO!A55)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A39=0," ",[1]COUNTRY_INFO!A39)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A56=0," ",[1]COUNTRY_INFO!A56)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A40=0," ",[1]COUNTRY_INFO!A40)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A57=0," ",[1]COUNTRY_INFO!A57)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A52=0," ",[1]COUNTRY_INFO!A52)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A53=0," ",[1]COUNTRY_INFO!A53)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A54=0," ",[1]COUNTRY_INFO!A54)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A55=0," ",[1]COUNTRY_INFO!A55)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A56=0," ",[1]COUNTRY_INFO!A56)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A57=0," ",[1]COUNTRY_INFO!A57)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="2" t="s">
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="e">
+        <f>IF([1]COUNTRY_INFO!A58=0," ",[1]COUNTRY_INFO!A58)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="str">
-        <f>IF([1]COUNTRY_INFO!A58=0," ",[1]COUNTRY_INFO!A58)</f>
-        <v>Congo</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState ref="A2:C20">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C20">
     <sortCondition ref="B2:B20"/>
     <sortCondition ref="C2:C20"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>